--- a/BugReports/BugReport.xlsx
+++ b/BugReports/BugReport.xlsx
@@ -857,7 +857,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -877,9 +877,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -941,21 +938,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1597,14 +1579,14 @@
       <c r="G2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -1625,14 +1607,14 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
@@ -1648,31 +1630,31 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="213" customHeight="1" spans="1:26">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>1</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="10" t="s">
+      <c r="C4" s="10"/>
+      <c r="D4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="13" t="s">
+      <c r="E4" s="11"/>
+      <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
@@ -1688,19 +1670,19 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="37" customHeight="1" spans="1:26">
-      <c r="A5" s="9"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
@@ -1716,19 +1698,19 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="36" customHeight="1" spans="1:26">
-      <c r="A6" s="9"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
@@ -1744,19 +1726,19 @@
       <c r="Z6" s="2"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="41" customHeight="1" spans="1:26">
-      <c r="A7" s="17"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
@@ -1772,19 +1754,19 @@
       <c r="Z7" s="2"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="57" customHeight="1" spans="1:26">
-      <c r="A8" s="21"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -1800,17 +1782,17 @@
       <c r="Z8" s="2"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="60" customHeight="1" spans="1:26">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
